--- a/outputs/reports/random_forest_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/random_forest_v1/feature_importance_top10.xlsx
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0699099314364416</v>
+        <v>0.07128537539281089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0699099314364416</v>
+        <v>0.07128537539281089</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=6.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.13%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -515,10 +515,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06522771266272298</v>
+        <v>0.06794269690533204</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06522771266272298</v>
+        <v>0.06794269690533204</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.52%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.79%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.06257466028351776</v>
+        <v>0.06032811954240906</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06257466028351776</v>
+        <v>0.06032811954240906</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.26%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.03%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05371746488869882</v>
+        <v>0.05352744284457885</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05371746488869882</v>
+        <v>0.05352744284457885</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.37%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05359413285871334</v>
+        <v>0.05347886914881447</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05359413285871334</v>
+        <v>0.05347886914881447</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05314864471147066</v>
+        <v>0.05220979045101741</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05314864471147066</v>
+        <v>0.05220979045101741</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.31%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.22%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.05015250059614454</v>
+        <v>0.04822499703852008</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05015250059614454</v>
+        <v>0.04822499703852008</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.02%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.82%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04274640347258525</v>
+        <v>0.04229378740443412</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04274640347258525</v>
+        <v>0.04229378740443412</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.27%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03684917303412914</v>
+        <v>0.03490214011419904</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03684917303412914</v>
+        <v>0.03490214011419904</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.68%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.49%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02912809723430759</v>
+        <v>0.02968403128616421</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02912809723430759</v>
+        <v>0.02968403128616421</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.91%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.97%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/random_forest_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/random_forest_v1/feature_importance_top10.xlsx
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07128537539281089</v>
+        <v>0.07123498568589968</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07128537539281089</v>
+        <v>0.07123498568589968</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.13%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -515,10 +515,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06794269690533204</v>
+        <v>0.06438996081869364</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06794269690533204</v>
+        <v>0.06438996081869364</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.79%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.44%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.06032811954240906</v>
+        <v>0.05839048873031386</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06032811954240906</v>
+        <v>0.05839048873031386</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.03%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05352744284457885</v>
+        <v>0.05427018714487944</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05352744284457885</v>
+        <v>0.05427018714487944</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.43%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05347886914881447</v>
+        <v>0.05358114621860463</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05347886914881447</v>
+        <v>0.05358114621860463</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05220979045101741</v>
+        <v>0.05098330684009479</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05220979045101741</v>
+        <v>0.05098330684009479</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.22%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.10%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04822499703852008</v>
+        <v>0.04893369782155989</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04822499703852008</v>
+        <v>0.04893369782155989</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.82%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04229378740443412</v>
+        <v>0.04303240847945023</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04229378740443412</v>
+        <v>0.04303240847945023</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03490214011419904</v>
+        <v>0.03644836213775499</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03490214011419904</v>
+        <v>0.03644836213775499</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.49%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.64%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02968403128616421</v>
+        <v>0.02993899235451626</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02968403128616421</v>
+        <v>0.02993899235451626</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.97%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/random_forest_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/random_forest_v1/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07123498568589968</v>
+        <v>0.07861920191648994</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07123498568589968</v>
+        <v>0.07861920191648994</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.86%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06438996081869364</v>
+        <v>0.0532840740558066</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06438996081869364</v>
+        <v>0.0532840740558066</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.44%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.33%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05839048873031386</v>
+        <v>0.053014598924571</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05839048873031386</v>
+        <v>0.053014598924571</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=5.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05427018714487944</v>
+        <v>0.05061020905280734</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05427018714487944</v>
+        <v>0.05061020905280734</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.43%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=5.06%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05358114621860463</v>
+        <v>0.04959939767759144</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05358114621860463</v>
+        <v>0.04959939767759144</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.96%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05098330684009479</v>
+        <v>0.03354108819730399</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05098330684009479</v>
+        <v>0.03354108819730399</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.10%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04893369782155989</v>
+        <v>0.03143857980808221</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04893369782155989</v>
+        <v>0.03143857980808221</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.14%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04303240847945023</v>
+        <v>0.03080299006641432</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04303240847945023</v>
+        <v>0.03080299006641432</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.08%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03644836213775499</v>
+        <v>0.02956599781773235</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03644836213775499</v>
+        <v>0.02956599781773235</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.64%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.96%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02993899235451626</v>
+        <v>0.02851796918745795</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02993899235451626</v>
+        <v>0.02851796918745795</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=2.85%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
